--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123569110</v>
+        <v>123565189</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>95150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossen, Mossen, Srm</t>
+          <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650048</v>
+        <v>649711</v>
       </c>
       <c r="R2" t="n">
-        <v>6572489</v>
+        <v>6572611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123565189</v>
+        <v>123569110</v>
       </c>
       <c r="B3" t="n">
-        <v>95150</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjurfällan, Tjurfällan, Srm</t>
+          <t>Mossen, Mossen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649711</v>
+        <v>650048</v>
       </c>
       <c r="R3" t="n">
-        <v>6572611</v>
+        <v>6572489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123560720</v>
+        <v>123561588</v>
       </c>
       <c r="B12" t="n">
-        <v>95150</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,38 +1837,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649116</v>
+        <v>649193</v>
       </c>
       <c r="R12" t="n">
-        <v>6572828</v>
+        <v>6572754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123561588</v>
+        <v>123560720</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>95150</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,52 +1963,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649193</v>
+        <v>649116</v>
       </c>
       <c r="R13" t="n">
-        <v>6572754</v>
+        <v>6572828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123565189</v>
+        <v>123561724</v>
       </c>
       <c r="B2" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>649711</v>
+        <v>649185</v>
       </c>
       <c r="R2" t="n">
-        <v>6572611</v>
+        <v>6572747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123569110</v>
+        <v>123560248</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossen, Mossen, Srm</t>
+          <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650048</v>
+        <v>649010</v>
       </c>
       <c r="R3" t="n">
-        <v>6572489</v>
+        <v>6572865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123562823</v>
+        <v>123565697</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjurfällan, Tjurfällan, Srm</t>
+          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649364</v>
+        <v>649764</v>
       </c>
       <c r="R4" t="n">
-        <v>6572835</v>
+        <v>6572613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123560248</v>
+        <v>123559653</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>57638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1033,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649010</v>
+        <v>648874</v>
       </c>
       <c r="R5" t="n">
-        <v>6572865</v>
+        <v>6572964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123565697</v>
+        <v>123569110</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
+          <t>Mossen, Mossen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649764</v>
+        <v>650048</v>
       </c>
       <c r="R6" t="n">
-        <v>6572613</v>
+        <v>6572489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123561724</v>
+        <v>123565189</v>
       </c>
       <c r="B7" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649185</v>
+        <v>649711</v>
       </c>
       <c r="R7" t="n">
-        <v>6572747</v>
+        <v>6572611</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1370,7 @@
         <v>123560842</v>
       </c>
       <c r="B8" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123565497</v>
+        <v>123561588</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,38 +1491,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649729</v>
+        <v>649193</v>
       </c>
       <c r="R9" t="n">
-        <v>6572610</v>
+        <v>6572754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123559654</v>
+        <v>123565497</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>91003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,43 +1617,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648874</v>
+        <v>649729</v>
       </c>
       <c r="R10" t="n">
-        <v>6572964</v>
+        <v>6572610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123559653</v>
+        <v>123560720</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>95167</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,43 +1729,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648874</v>
+        <v>649116</v>
       </c>
       <c r="R11" t="n">
-        <v>6572964</v>
+        <v>6572828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123561588</v>
+        <v>123562823</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,40 +1841,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649193</v>
+        <v>649364</v>
       </c>
       <c r="R12" t="n">
-        <v>6572754</v>
+        <v>6572835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123560720</v>
+        <v>123559654</v>
       </c>
       <c r="B13" t="n">
-        <v>95150</v>
+        <v>57857</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,34 +1962,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649116</v>
+        <v>648874</v>
       </c>
       <c r="R13" t="n">
-        <v>6572828</v>
+        <v>6572964</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123561724</v>
+        <v>123560842</v>
       </c>
       <c r="B2" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>649185</v>
+        <v>649128</v>
       </c>
       <c r="R2" t="n">
-        <v>6572747</v>
+        <v>6572798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>123560248</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123565697</v>
+        <v>123569110</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
+          <t>Mossen, Mossen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649764</v>
+        <v>650048</v>
       </c>
       <c r="R4" t="n">
-        <v>6572613</v>
+        <v>6572489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123559653</v>
+        <v>123562823</v>
       </c>
       <c r="B5" t="n">
-        <v>57638</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648874</v>
+        <v>649364</v>
       </c>
       <c r="R5" t="n">
-        <v>6572964</v>
+        <v>6572835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123569110</v>
+        <v>123561724</v>
       </c>
       <c r="B6" t="n">
-        <v>57503</v>
+        <v>95173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,43 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mossen, Mossen, Srm</t>
+          <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650048</v>
+        <v>649185</v>
       </c>
       <c r="R6" t="n">
-        <v>6572489</v>
+        <v>6572747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123565189</v>
+        <v>123559653</v>
       </c>
       <c r="B7" t="n">
-        <v>95167</v>
+        <v>57641</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,38 +1262,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649711</v>
+        <v>648874</v>
       </c>
       <c r="R7" t="n">
-        <v>6572611</v>
+        <v>6572964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123560842</v>
+        <v>123565189</v>
       </c>
       <c r="B8" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649128</v>
+        <v>649711</v>
       </c>
       <c r="R8" t="n">
-        <v>6572798</v>
+        <v>6572611</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123561588</v>
+        <v>123565697</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,52 +1491,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjurfällan, Tjurfällan, Srm</t>
+          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649193</v>
+        <v>649764</v>
       </c>
       <c r="R9" t="n">
-        <v>6572754</v>
+        <v>6572613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123565497</v>
+        <v>123561588</v>
       </c>
       <c r="B10" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,38 +1608,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649729</v>
+        <v>649193</v>
       </c>
       <c r="R10" t="n">
-        <v>6572610</v>
+        <v>6572754</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123560720</v>
+        <v>123559654</v>
       </c>
       <c r="B11" t="n">
-        <v>95167</v>
+        <v>57860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,34 +1738,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649116</v>
+        <v>648874</v>
       </c>
       <c r="R11" t="n">
-        <v>6572828</v>
+        <v>6572964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123562823</v>
+        <v>123565497</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,39 +1855,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649364</v>
+        <v>649729</v>
       </c>
       <c r="R12" t="n">
-        <v>6572835</v>
+        <v>6572610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123559654</v>
+        <v>123560720</v>
       </c>
       <c r="B13" t="n">
-        <v>57857</v>
+        <v>95173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,39 +1967,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648874</v>
+        <v>649116</v>
       </c>
       <c r="R13" t="n">
-        <v>6572964</v>
+        <v>6572828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123560842</v>
       </c>
       <c r="B2" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123560248</v>
+        <v>123559653</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649010</v>
+        <v>648874</v>
       </c>
       <c r="R3" t="n">
-        <v>6572865</v>
+        <v>6572964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123569110</v>
+        <v>123561588</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +916,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossen, Mossen, Srm</t>
+          <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650048</v>
+        <v>649193</v>
       </c>
       <c r="R4" t="n">
-        <v>6572489</v>
+        <v>6572754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123562823</v>
+        <v>123565189</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>95175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,43 +1042,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649364</v>
+        <v>649711</v>
       </c>
       <c r="R5" t="n">
-        <v>6572835</v>
+        <v>6572611</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123561724</v>
+        <v>123560720</v>
       </c>
       <c r="B6" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649185</v>
+        <v>649116</v>
       </c>
       <c r="R6" t="n">
-        <v>6572747</v>
+        <v>6572828</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123559653</v>
+        <v>123559654</v>
       </c>
       <c r="B7" t="n">
-        <v>57641</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,20 +1266,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123565189</v>
+        <v>123565497</v>
       </c>
       <c r="B8" t="n">
-        <v>95173</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649711</v>
+        <v>649729</v>
       </c>
       <c r="R8" t="n">
-        <v>6572611</v>
+        <v>6572610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123565697</v>
+        <v>123560248</v>
       </c>
       <c r="B9" t="n">
-        <v>57643</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,43 +1495,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
+          <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649764</v>
+        <v>649010</v>
       </c>
       <c r="R9" t="n">
-        <v>6572613</v>
+        <v>6572865</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123561588</v>
+        <v>123561724</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>95175</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,52 +1612,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649193</v>
+        <v>649185</v>
       </c>
       <c r="R10" t="n">
-        <v>6572754</v>
+        <v>6572747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123559654</v>
+        <v>123569110</v>
       </c>
       <c r="B11" t="n">
-        <v>57860</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,20 +1724,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1758,19 +1748,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjurfällan, Tjurfällan, Srm</t>
+          <t>Mossen, Mossen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648874</v>
+        <v>650048</v>
       </c>
       <c r="R11" t="n">
-        <v>6572964</v>
+        <v>6572489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123565497</v>
+        <v>123565697</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,34 +1845,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjurfällan, Tjurfällan, Srm</t>
+          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649729</v>
+        <v>649764</v>
       </c>
       <c r="R12" t="n">
-        <v>6572610</v>
+        <v>6572613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123560720</v>
+        <v>123562823</v>
       </c>
       <c r="B13" t="n">
-        <v>95173</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,38 +1958,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649116</v>
+        <v>649364</v>
       </c>
       <c r="R13" t="n">
-        <v>6572828</v>
+        <v>6572835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -1829,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123565697</v>
+        <v>123562823</v>
       </c>
       <c r="B12" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,39 +1845,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
+          <t>Tjurfällan, Tjurfällan, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649764</v>
+        <v>649364</v>
       </c>
       <c r="R12" t="n">
-        <v>6572613</v>
+        <v>6572835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123562823</v>
+        <v>123565697</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,39 +1962,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjurfällan, Tjurfällan, Srm</t>
+          <t>Flaggstångsberget, Flaggstångsberget, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649364</v>
+        <v>649764</v>
       </c>
       <c r="R13" t="n">
-        <v>6572835</v>
+        <v>6572613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,6 +2061,131 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129841994</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjurfällan (*knärot* /stjälk/), Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>649194</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6572753</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>AB-Sal-0016</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tjurfällan, Obskoord: 6573225/1603353/10 m ().</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6162-2025 artfynd.xlsx
+++ b/artfynd/A 6162-2025 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>129841994</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
